--- a/SDEM/Quiz/qUIZ.xlsx
+++ b/SDEM/Quiz/qUIZ.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Work\Training\SDEM\Quiz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Career\SDEM\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{663C6C50-FA04-443D-AD18-4D216D7DB5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A6CF57-56BE-423A-9D42-E8D3634FC931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{45709E7E-7F33-41CA-B1D5-8D053F27C29B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{45709E7E-7F33-41CA-B1D5-8D053F27C29B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$L$63</definedName>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="104">
   <si>
     <t xml:space="preserve">Which is the correct one about the business category in requirement definition, development, operation test and transition process? Choose one answer from following: </t>
   </si>
@@ -194,13 +195,177 @@
   </si>
   <si>
     <t>X</t>
+  </si>
+  <si>
+    <t>ザカリー</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Main Phase</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>PG</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>OM</t>
+  </si>
+  <si>
+    <t>IT Vision Planning</t>
+  </si>
+  <si>
+    <t>System Planning</t>
+  </si>
+  <si>
+    <t>Current Business and System Analysis</t>
+  </si>
+  <si>
+    <t>System Resource Definition</t>
+  </si>
+  <si>
+    <t>User Interface Design</t>
+  </si>
+  <si>
+    <t>System Structure Design</t>
+  </si>
+  <si>
+    <t>Program Structure Design</t>
+  </si>
+  <si>
+    <t>Programming</t>
+  </si>
+  <si>
+    <t>Program Test</t>
+  </si>
+  <si>
+    <t>Integration Test</t>
+  </si>
+  <si>
+    <t>System Test</t>
+  </si>
+  <si>
+    <t>Operational Test and Transition</t>
+  </si>
+  <si>
+    <t>Operation and Maintenance</t>
+  </si>
+  <si>
+    <t>Planning Process</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
+    <t>Requirement Definition Process</t>
+  </si>
+  <si>
+    <t>Requirement Definition</t>
+  </si>
+  <si>
+    <t>Development Process</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Operational Test and Transition Process</t>
+  </si>
+  <si>
+    <t>Operation and Maintenance Process</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Program module</t>
+  </si>
+  <si>
+    <t>Verification by developers
+&lt;-------------------------------&gt;
+Verification</t>
+  </si>
+  <si>
+    <t>Verification by designer
+&lt;------------------------------------------------------&gt;
+Verification</t>
+  </si>
+  <si>
+    <t>Validation by users
+&lt;--------------------------------------------------------------------------&gt;
+Validation</t>
+  </si>
+  <si>
+    <t>Evaluation by top management
+&lt;--------------------------------------------------------------------------------------------------------&gt;
+Evaluation</t>
+  </si>
+  <si>
+    <t>Gradually decompose in requirement definition/design</t>
+  </si>
+  <si>
+    <t>Gradually integrate in testing</t>
+  </si>
+  <si>
+    <t>System component</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,8 +380,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -241,8 +435,31 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -250,11 +467,393 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="mediumDashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,21 +864,184 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -614,16 +1376,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D078CB8-B716-44DC-8984-1D4AFE7302BF}">
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="4" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="3.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="3.28515625" style="6" customWidth="1"/>
-    <col min="8" max="9" width="3.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="3.7109375" style="6" customWidth="1"/>
+    <col min="5" max="7" width="3.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="3.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="174" style="4" customWidth="1"/>
   </cols>
@@ -641,7 +1402,7 @@
       <c r="F1" s="1">
         <v>50</v>
       </c>
-      <c r="G1" s="6">
+      <c r="G1" s="1">
         <v>60</v>
       </c>
       <c r="H1" s="1">
@@ -659,35 +1420,35 @@
         <v>61</v>
       </c>
       <c r="C2" s="1">
-        <f>COUNTIF(C4:C62,"O")</f>
+        <f t="shared" ref="C2:J2" si="0">COUNTIF(C4:C62,"O")</f>
         <v>10</v>
       </c>
       <c r="D2" s="1">
-        <f>COUNTIF(D4:D62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E2" s="1">
-        <f>COUNTIF(E4:E62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="F2" s="1">
-        <f>COUNTIF(F4:F62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <f>COUNTIF(G4:G62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="H2" s="1">
-        <f>COUNTIF(H4:H62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I2" s="1">
-        <f>COUNTIF(I4:I62,"O")</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="J2" s="1">
-        <f>COUNTIF(J4:J62,"O")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -703,7 +1464,7 @@
       <c r="B4">
         <v>13</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -740,7 +1501,7 @@
       <c r="F6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -796,7 +1557,7 @@
       <c r="B10">
         <v>7</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -819,7 +1580,7 @@
       <c r="F11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -889,7 +1650,7 @@
       <c r="B16">
         <v>37</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -940,7 +1701,7 @@
       <c r="F19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -982,7 +1743,7 @@
       <c r="B22">
         <v>25</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1047,7 +1808,7 @@
       <c r="F26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H26" s="1" t="s">
@@ -1076,7 +1837,7 @@
       <c r="B28">
         <v>43</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="6" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1127,7 +1888,7 @@
       <c r="F31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H31" s="1" t="s">
@@ -1169,7 +1930,7 @@
       <c r="B34">
         <v>31</v>
       </c>
-      <c r="K34" s="7" t="s">
+      <c r="K34" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1234,7 +1995,7 @@
       <c r="F38" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H38" s="1" t="s">
@@ -1262,7 +2023,7 @@
       <c r="B40">
         <v>1</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="6" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1285,7 +2046,7 @@
       <c r="F41" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H41" s="1" t="s">
@@ -1355,7 +2116,7 @@
       <c r="B46">
         <v>55</v>
       </c>
-      <c r="K46" s="7" t="s">
+      <c r="K46" s="6" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1420,7 +2181,7 @@
       <c r="F50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H50" s="1" t="s">
@@ -1448,7 +2209,7 @@
       <c r="B52">
         <v>49</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1468,7 +2229,7 @@
       <c r="F53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H53" s="1" t="s">
@@ -1522,10 +2283,10 @@
       <c r="E56" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="H56" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K56" t="s">
@@ -1550,7 +2311,7 @@
       <c r="B58">
         <v>19</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="6" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1640,6 +2401,11 @@
       </c>
       <c r="B63">
         <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L64" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1647,6 +2413,413 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:L62">
     <sortCondition ref="K4:K62"/>
   </sortState>
+  <conditionalFormatting sqref="L64">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>ROW()=CELL("row")</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(L64))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52326DD5-7A34-4480-8A0B-D8069C4A2E34}">
+  <dimension ref="A1:AC20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.28515625" customWidth="1"/>
+    <col min="20" max="20" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" ht="60.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="12"/>
+      <c r="F1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="15"/>
+      <c r="F2" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="25"/>
+      <c r="M2" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:29" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="Q9" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="R9" s="32"/>
+      <c r="S9" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="33"/>
+      <c r="U9" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="V9" s="32"/>
+      <c r="W9" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC9" s="35" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q10" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="R10" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="T10" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="U10" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="V10" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="W10" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="X10" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y10" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA10" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB10" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC10" s="44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P11" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="R11" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="S11" s="45"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
+      <c r="V11" s="45"/>
+      <c r="W11" s="45"/>
+      <c r="X11" s="45"/>
+      <c r="Y11" s="45"/>
+      <c r="Z11" s="45"/>
+      <c r="AA11" s="45"/>
+      <c r="AB11" s="46"/>
+      <c r="AC11" s="51" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P12" s="29"/>
+      <c r="R12" s="52" t="s">
+        <v>93</v>
+      </c>
+      <c r="S12" s="53"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="47"/>
+      <c r="AA12" s="48"/>
+      <c r="AB12" s="55" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="R13" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="S13" s="39"/>
+      <c r="U13" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="V13" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="W13" s="47"/>
+      <c r="X13" s="47"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="48"/>
+      <c r="AA13" s="51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="48.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="28"/>
+      <c r="P14" s="29"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="39"/>
+      <c r="V14" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="W14" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="X14" s="47"/>
+      <c r="Y14" s="48"/>
+      <c r="Z14" s="51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P15" s="29"/>
+      <c r="R15" s="36"/>
+      <c r="S15" s="37"/>
+      <c r="W15" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="42"/>
+    </row>
+    <row r="16" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AB16" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC16" s="54"/>
+    </row>
+    <row r="17" spans="21:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="21:28" x14ac:dyDescent="0.25">
+      <c r="U18" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="V18" s="56"/>
+      <c r="Z18" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA18" s="56"/>
+      <c r="AB18" s="56"/>
+    </row>
+    <row r="19" spans="21:28" x14ac:dyDescent="0.25">
+      <c r="U19" s="56"/>
+      <c r="V19" s="56"/>
+      <c r="Z19" s="56"/>
+      <c r="AA19" s="56"/>
+      <c r="AB19" s="56"/>
+    </row>
+    <row r="20" spans="21:28" x14ac:dyDescent="0.25">
+      <c r="U20" s="56"/>
+      <c r="V20" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="Z18:AB19"/>
+    <mergeCell ref="AB16:AC16"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="U18:V20"/>
+    <mergeCell ref="R13:S15"/>
+    <mergeCell ref="V13:Z13"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="W15:Y15"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="U12:AA12"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="W9:Y9"/>
+    <mergeCell ref="Z9:AA9"/>
+    <mergeCell ref="R11:AB11"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:L2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/SDEM/Quiz/qUIZ.xlsx
+++ b/SDEM/Quiz/qUIZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Career\SDEM\Quiz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\New Documents\Zachary\Documents\SDEM\Quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A6CF57-56BE-423A-9D42-E8D3634FC931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D41157-611E-40F7-A9D8-03584F745C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{45709E7E-7F33-41CA-B1D5-8D053F27C29B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="1" xr2:uid="{45709E7E-7F33-41CA-B1D5-8D053F27C29B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$3:$L$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$4:$R$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="114">
   <si>
     <t xml:space="preserve">Which is the correct one about the business category in requirement definition, development, operation test and transition process? Choose one answer from following: </t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>O</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>ザカリー</t>
@@ -359,13 +356,46 @@
   </si>
   <si>
     <t>System component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is NOT the correct one about applying SDEM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is NOT the correct one about making the quality </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is NOT the correct one about relationship between SDEM and international standards </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is NOT the correct one about scope of tasks in system developing shown with SDEM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is the correct one about ST phases </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is the correct one about the business category in requirement definition, development, operation test and transition process </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is the correct one about the explanation of WBS (the definition in SDEM) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is the correct one about UI phase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which is the correct one about V-shaped model for quality assurance </t>
+  </si>
+  <si>
+    <t>Which is NOT the correct one about SDEM</t>
+  </si>
+  <si>
+    <t>Same</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,8 +439,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,6 +515,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -853,15 +928,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -886,36 +958,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -928,35 +1060,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -964,11 +1093,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -979,11 +1111,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -991,35 +1123,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1376,1052 +1513,1418 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D078CB8-B716-44DC-8984-1D4AFE7302BF}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="3.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="10" width="3.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="174" style="4" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.28515625" style="72" customWidth="1"/>
+    <col min="5" max="6" width="3.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="3.28515625" style="72" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="31" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="3.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="3.28515625" style="1" customWidth="1"/>
+    <col min="12" max="15" width="3.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="3.28515625" style="72" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="174" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="C1" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1" s="72">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1">
+        <v>4</v>
+      </c>
+      <c r="G1" s="72">
+        <v>5</v>
+      </c>
+      <c r="H1" s="30">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
+        <v>13</v>
+      </c>
+      <c r="P1" s="72">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C2" s="1">
         <v>60</v>
       </c>
-      <c r="D1" s="1">
+      <c r="D2" s="73">
         <v>70</v>
       </c>
-      <c r="E1" s="1">
+      <c r="E2" s="1">
         <v>60</v>
       </c>
-      <c r="F1" s="1">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1">
+      <c r="F2" s="1">
+        <v>50</v>
+      </c>
+      <c r="G2" s="72">
         <v>60</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H2" s="30">
         <v>60</v>
       </c>
-      <c r="I1" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="I2" s="1">
+        <v>50</v>
+      </c>
+      <c r="J2" s="1">
+        <v>50</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="1">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1">
+        <v>50</v>
+      </c>
+      <c r="N2" s="1">
+        <v>50</v>
+      </c>
+      <c r="O2" s="1">
+        <v>50</v>
+      </c>
+      <c r="P2" s="72">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>62</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>61</v>
       </c>
-      <c r="C2" s="1">
-        <f t="shared" ref="C2:J2" si="0">COUNTIF(C4:C62,"O")</f>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:J3" si="0">COUNTIF(C5:C63,"O")</f>
         <v>10</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D3" s="72">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E3" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F3" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" s="72">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H3" s="30">
+        <f>COUNTIF(H5:H62,"O")</f>
+        <v>10</v>
+      </c>
+      <c r="I3" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J3" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="J2" s="1">
-        <f t="shared" si="0"/>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3" si="1">COUNTIF(K5:K63,"O")</f>
+        <v>10</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:M3" si="2">COUNTIF(L5:L63,"O")</f>
+        <v>10</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N3" s="1">
+        <f t="shared" ref="N3:P3" si="3">COUNTIF(N5:N63,"O")</f>
+        <v>10</v>
+      </c>
+      <c r="O3" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="P3" s="72">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" s="35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>10</v>
+      </c>
+      <c r="R6" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="S6">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P7" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="S7">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="Q9" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P12" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="Q13" t="s">
+        <v>5</v>
+      </c>
+      <c r="R13" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="R17" s="35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>38</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <v>39</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>30</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P20" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>30</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>41</v>
+      </c>
+      <c r="N21" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="O21" s="34"/>
+      <c r="Q21" t="s">
+        <v>30</v>
+      </c>
+      <c r="R21" s="36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>26</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="Q26" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>29</v>
+      </c>
+      <c r="C27" s="75"/>
+      <c r="D27" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="I27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="O27" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="P27" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" s="35" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>44</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>45</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>29</v>
+      </c>
+      <c r="B32">
+        <v>46</v>
+      </c>
+      <c r="C32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H32" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="K32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="75"/>
+      <c r="N32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="O32" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="P32" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <v>47</v>
+      </c>
+      <c r="M33" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="Q33" t="s">
+        <v>35</v>
+      </c>
+      <c r="R33" s="36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>32</v>
+      </c>
+      <c r="B35">
+        <v>31</v>
+      </c>
+      <c r="Q35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="R35" s="35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>33</v>
+      </c>
+      <c r="B36">
+        <v>32</v>
+      </c>
+      <c r="O36" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>25</v>
+      </c>
+      <c r="R36" s="36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37">
+        <v>33</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>25</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>35</v>
+      </c>
+      <c r="B38">
+        <v>34</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>36</v>
+      </c>
+      <c r="B39">
+        <v>35</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="H39" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P39" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>38</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="R41" s="33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>39</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="G42" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="J42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="75"/>
+      <c r="L42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="N42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="O42" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="P42" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>40</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>13</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5">
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6">
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45">
+        <v>5</v>
+      </c>
+      <c r="K45" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>0</v>
+      </c>
+      <c r="R45" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>44</v>
+      </c>
+      <c r="B47">
+        <v>55</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R47" s="33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>56</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>45</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>57</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>45</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50">
+        <v>58</v>
+      </c>
+      <c r="J50" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>45</v>
+      </c>
+      <c r="R50" s="36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>48</v>
+      </c>
+      <c r="B51">
+        <v>59</v>
+      </c>
+      <c r="C51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="F51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="G51" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H51" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="I51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="J51" s="75"/>
+      <c r="K51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="L51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="N51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="O51" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="P51" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>45</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>50</v>
+      </c>
+      <c r="B53">
+        <v>49</v>
+      </c>
+      <c r="Q53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="R53" s="66" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <v>50</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P54" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>40</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55">
+        <v>51</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56">
+        <v>52</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>40</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" s="67" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="67">
+        <v>54</v>
+      </c>
+      <c r="B57" s="67">
+        <v>53</v>
+      </c>
+      <c r="C57" s="68"/>
+      <c r="D57" s="74"/>
+      <c r="E57" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="F57" s="68"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="68"/>
+      <c r="K57" s="68"/>
+      <c r="L57" s="68"/>
+      <c r="M57" s="68"/>
+      <c r="N57" s="68"/>
+      <c r="O57" s="68"/>
+      <c r="P57" s="74"/>
+      <c r="Q57" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="R57" s="70" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="E58" s="32"/>
+      <c r="I58" s="32"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>19</v>
+      </c>
+      <c r="Q59" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
+      <c r="R59" s="66" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>20</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K7" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8">
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>58</v>
+      </c>
+      <c r="B61">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>7</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>9</v>
-      </c>
-      <c r="K12" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="K13" t="s">
-        <v>5</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="K14" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>37</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17">
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>22</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H62" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I62" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q62" t="s">
         <v>15</v>
       </c>
-      <c r="B17">
-        <v>38</v>
-      </c>
-      <c r="K17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>39</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>40</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="R62" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20">
-        <v>41</v>
-      </c>
-      <c r="K20" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21">
+    </row>
+    <row r="63" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63">
+        <v>23</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="G63" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K63" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P63" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>15</v>
+      </c>
+      <c r="R63" s="27" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>25</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>26</v>
-      </c>
-      <c r="K23" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>27</v>
-      </c>
-      <c r="K24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>28</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K25" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>29</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>43</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29">
-        <v>44</v>
-      </c>
-      <c r="K29" t="s">
-        <v>35</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30">
-        <v>45</v>
-      </c>
-      <c r="K30" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31">
-        <v>46</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K31" t="s">
-        <v>35</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32">
-        <v>47</v>
-      </c>
-      <c r="K32" t="s">
-        <v>35</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34">
-        <v>31</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35">
-        <v>32</v>
-      </c>
-      <c r="K35" t="s">
-        <v>25</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>33</v>
-      </c>
-      <c r="K36" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37">
-        <v>34</v>
-      </c>
-      <c r="K37" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38">
-        <v>35</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K38" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K41" t="s">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>3</v>
-      </c>
-      <c r="K42" t="s">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43">
-        <v>4</v>
-      </c>
-      <c r="K43" t="s">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44">
-        <v>5</v>
-      </c>
-      <c r="K44" t="s">
-        <v>0</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46">
-        <v>55</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47">
-        <v>56</v>
-      </c>
-      <c r="K47" t="s">
-        <v>45</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48">
-        <v>57</v>
-      </c>
-      <c r="K48" t="s">
-        <v>45</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49">
-        <v>58</v>
-      </c>
-      <c r="K49" t="s">
-        <v>45</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>59</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K50" t="s">
-        <v>45</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52">
-        <v>49</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>61</v>
+      </c>
+      <c r="B64">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="17:18" x14ac:dyDescent="0.25">
+      <c r="R65" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B53">
-        <v>50</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K53" t="s">
-        <v>40</v>
-      </c>
-      <c r="L53" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54">
-        <v>51</v>
-      </c>
-      <c r="K54" t="s">
-        <v>40</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55">
-        <v>52</v>
-      </c>
-      <c r="K55" t="s">
-        <v>40</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56">
-        <v>53</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="K56" t="s">
-        <v>40</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>55</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58">
-        <v>19</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59">
-        <v>20</v>
-      </c>
-      <c r="K59" t="s">
-        <v>15</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60">
-        <v>21</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61">
-        <v>22</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62">
-        <v>23</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L64" s="7" t="s">
-        <v>52</v>
+    </row>
+    <row r="67" spans="17:18" x14ac:dyDescent="0.25">
+      <c r="Q67" s="71" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L63" xr:uid="{2D078CB8-B716-44DC-8984-1D4AFE7302BF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:L62">
-    <sortCondition ref="K4:K62"/>
+  <autoFilter ref="A4:R65" xr:uid="{2D078CB8-B716-44DC-8984-1D4AFE7302BF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:R63">
+    <sortCondition ref="Q5:Q63"/>
   </sortState>
-  <conditionalFormatting sqref="L64">
+  <conditionalFormatting sqref="R65">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>ROW()=CELL("row")</formula>
     </cfRule>
     <cfRule type="containsBlanks" dxfId="0" priority="2">
-      <formula>LEN(TRIM(L64))=0</formula>
+      <formula>LEN(TRIM(R65))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2450,346 +2953,346 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="60.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="39"/>
+      <c r="F1" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B2" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="11" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" s="44"/>
+      <c r="M2" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="16" t="s">
+      <c r="B3" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="N3" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="N2" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+    </row>
+    <row r="4" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="C4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="D4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="E4" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="F4" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G4" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="H4" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="I4" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="J4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="K4" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="27" t="s">
+      <c r="L4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="M4" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="N4" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:29" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="Q9" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="R9" s="32"/>
-      <c r="S9" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="T9" s="33"/>
-      <c r="U9" s="32" t="s">
+      <c r="Q9" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" s="46"/>
+      <c r="S9" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="T9" s="47"/>
+      <c r="U9" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="V9" s="46"/>
+      <c r="W9" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="V9" s="32"/>
-      <c r="W9" s="33" t="s">
+      <c r="X9" s="47"/>
+      <c r="Y9" s="47"/>
+      <c r="Z9" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="34" t="s">
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC9" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="AC9" s="35" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Q10" s="43" t="s">
+      <c r="Q10" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="R10" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="S10" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="S10" s="30" t="s">
+      <c r="T10" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="T10" s="30" t="s">
+      <c r="U10" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="U10" s="30" t="s">
+      <c r="V10" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="V10" s="30" t="s">
+      <c r="W10" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="W10" s="30" t="s">
+      <c r="X10" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="X10" s="30" t="s">
+      <c r="Y10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="Y10" s="30" t="s">
+      <c r="Z10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="Z10" s="30" t="s">
+      <c r="AA10" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="AA10" s="30" t="s">
+      <c r="AB10" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="AB10" s="30" t="s">
+      <c r="AC10" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="AC10" s="44" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="11" spans="1:29" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P11" s="29" t="s">
+      <c r="P11" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="Q11" s="51" t="s">
+      <c r="R11" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" s="64"/>
+      <c r="T11" s="64"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="64"/>
+      <c r="AA11" s="64"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P12" s="51"/>
+      <c r="R12" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="S12" s="62"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="V12" s="57"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="58"/>
+      <c r="AB12" s="26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="R11" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="45"/>
-      <c r="AA11" s="45"/>
-      <c r="AB11" s="46"/>
-      <c r="AC11" s="51" t="s">
+      <c r="R13" s="52" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="48" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P12" s="29"/>
-      <c r="R12" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="S12" s="53"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="48"/>
-      <c r="AB12" s="55" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P13" s="29" t="s">
+      <c r="S13" s="53"/>
+      <c r="U13" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="V13" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="W13" s="57"/>
+      <c r="X13" s="57"/>
+      <c r="Y13" s="57"/>
+      <c r="Z13" s="58"/>
+      <c r="AA13" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="48.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="19"/>
+      <c r="P14" s="51"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="53"/>
+      <c r="V14" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="W14" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="58"/>
+      <c r="Z14" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P15" s="51"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="55"/>
+      <c r="W15" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="R13" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="S13" s="39"/>
-      <c r="U13" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="V13" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="51" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:29" ht="48.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I14" s="28"/>
-      <c r="P14" s="29"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="39"/>
-      <c r="V14" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="W14" s="50" t="s">
-        <v>97</v>
-      </c>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="48"/>
-      <c r="Z14" s="51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P15" s="29"/>
-      <c r="R15" s="36"/>
-      <c r="S15" s="37"/>
-      <c r="W15" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="42"/>
+      <c r="X15" s="60"/>
+      <c r="Y15" s="61"/>
     </row>
     <row r="16" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="AB16" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="AC16" s="54"/>
+      <c r="AB16" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC16" s="50"/>
     </row>
     <row r="17" spans="21:28" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="21:28" x14ac:dyDescent="0.25">
-      <c r="U18" s="56" t="s">
+      <c r="U18" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="V18" s="48"/>
+      <c r="Z18" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="V18" s="56"/>
-      <c r="Z18" s="56" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA18" s="56"/>
-      <c r="AB18" s="56"/>
+      <c r="AA18" s="48"/>
+      <c r="AB18" s="48"/>
     </row>
     <row r="19" spans="21:28" x14ac:dyDescent="0.25">
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="Z19" s="56"/>
-      <c r="AA19" s="56"/>
-      <c r="AB19" s="56"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
     </row>
     <row r="20" spans="21:28" x14ac:dyDescent="0.25">
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2804,12 +3307,12 @@
     <mergeCell ref="W15:Y15"/>
     <mergeCell ref="R12:T12"/>
     <mergeCell ref="U12:AA12"/>
+    <mergeCell ref="R11:AB11"/>
     <mergeCell ref="Q9:R9"/>
     <mergeCell ref="S9:T9"/>
     <mergeCell ref="U9:V9"/>
     <mergeCell ref="W9:Y9"/>
     <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="R11:AB11"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D1:E1"/>
